--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_79_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_79_IN_Piura.xlsx
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>22.93</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>47.38</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>29.35</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.34</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1916,11 +1916,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>94.8117</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>66.6599</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>70.31</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>28.1518</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>29.69</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2145,11 +2145,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>94.8345</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2268,6 +2268,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2385,6 +2386,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2429,6 +2431,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2648,11 +2651,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>109.99</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2662,19 +2665,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>28.39</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.5894</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>85.62</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>16.61</v>
       </c>
     </row>
     <row r="13"/>
